--- a/data/trans_orig/IP12_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP12_2023-Habitat-trans_orig.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables originales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2023" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,12 +524,18 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si en las últimas 2 semanas limitaron su actividad por dolores o síntomas en 2023 (Tasa respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas limitaron su actividad por dolores o síntomas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -542,24 +548,30 @@
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="n"/>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
       <c r="K1" s="3" t="n"/>
       <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
+      <c r="M1" s="3" t="n"/>
       <c r="N1" s="3" t="n"/>
       <c r="O1" s="3" t="n"/>
       <c r="P1" s="3" t="n"/>
-      <c r="Q1" s="3" t="n"/>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="n"/>
+      <c r="S1" s="3" t="n"/>
+      <c r="T1" s="3" t="n"/>
+      <c r="U1" s="3" t="n"/>
+      <c r="V1" s="3" t="n"/>
+      <c r="W1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,65 +588,95 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>n (muestra)</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>N (estimada)</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím inf IC)</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>N (lím sup IC)</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>Estimación puntual</t>
         </is>
       </c>
-      <c r="P2" s="3" t="inlineStr">
+      <c r="V2" s="3" t="inlineStr">
         <is>
           <t>lím inf IC</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="inlineStr">
+      <c r="W2" s="3" t="inlineStr">
         <is>
           <t>lím sup IC</t>
         </is>
@@ -658,6 +700,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="n"/>
       <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="n"/>
+      <c r="U3" s="2" t="n"/>
+      <c r="V3" s="2" t="n"/>
+      <c r="W3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -667,70 +715,112 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>8853</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4557</t>
+        </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>8855</v>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>7378</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>17707</v>
+          <t>3791</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>13346</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>11936</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>7266</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>18345</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -738,70 +828,112 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>180</v>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>108427</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4295</t>
+        </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>9552</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>131557</v>
+          <t>3,66%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8,14%</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>337</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>239986</v>
+          <t>424</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4674</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>5771</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2888</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>11943</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -809,216 +941,342 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>196</v>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>117280</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>108427</t>
+        </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>101971</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>112252</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>171</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>140412</v>
+          <t>92,45%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>86,95%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>157</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>131557</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>367</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>257693</v>
+          <t>124561</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>135476</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>93,69%</t>
+        </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>239986</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>232492</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>245924</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>93,13%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>90,22%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>95,43%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
+      <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>13592</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>117280</t>
+        </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>117280</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>117280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>17222</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>171</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>140412</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>47</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>30814</v>
+          <t>140412</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>140412</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>257693</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>257693</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>257693</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>258</v>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>176920</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9833</t>
+        </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>5658</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>16298</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>318</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>237813</v>
+          <t>5,16%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>576</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>414734</v>
+          <t>7858</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>20041</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>22942</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>15954</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>32106</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -1026,145 +1284,225 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="n">
-        <v>280</v>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>190512</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3759</t>
+        </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>1617</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>7556</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>343</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>255035</v>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>623</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>445548</v>
+          <t>1146</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>9341</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>7872</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>4083</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>14476</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>14514</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>176920</t>
+        </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>170378</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>182026</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>19</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>16077</v>
+          <t>92,87%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>89,43%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>95,55%</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>318</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>237813</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>42</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>30592</v>
+          <t>229821</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>243863</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>93,25%</t>
+        </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>576</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>414734</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>404875</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>422959</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>93,08%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>90,87%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>94,93%</t>
         </is>
       </c>
     </row>
@@ -1172,216 +1510,342 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>203</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>175071</v>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>190512</t>
+        </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>190512</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>190512</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>206</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>169209</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>343</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>255035</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>409</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>344279</v>
+          <t>255035</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>255035</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>445548</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>445548</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>445548</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n"/>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>226</v>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>189585</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8570</t>
+        </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>14150</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>225</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>185286</v>
+          <t>4,52%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11998</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>451</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>374871</v>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>22832</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>20568</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>13223</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>32763</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
+      <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="n">
-        <v>16</v>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>10313</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5944</t>
+        </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>2548</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>22</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>16950</v>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>4080</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
-        <v>38</v>
-      </c>
-      <c r="N13" s="2" t="n">
-        <v>27263</v>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9424</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>5559</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>17105</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -1392,67 +1856,109 @@
           <t>No</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n">
-        <v>224</v>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>157649</v>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>175071</t>
+        </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>167932</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>181530</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>216</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>164288</v>
+          <t>92,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>95,75%</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>206</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>169209</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>440</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>321938</v>
+          <t>158381</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>175179</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>91,32%</t>
+        </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>409</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>344279</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>331975</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>353215</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>91,84%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>88,56%</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -1463,20 +1969,24 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="C15" s="2" t="n">
-        <v>240</v>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>167962</v>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>189585</t>
+        </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>189585</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>189585</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1484,32 +1994,40 @@
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="n">
-        <v>238</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>181238</v>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>225</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>185286</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="n">
-        <v>478</v>
-      </c>
-      <c r="N15" s="2" t="n">
-        <v>349201</v>
+          <t>185286</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>185286</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1522,6 +2040,36 @@
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>374871</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>374871</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>374871</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
@@ -1530,75 +2078,117 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Capitales</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="n">
-        <v>77</v>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>47272</v>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9590</t>
+        </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>14603</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>59103</v>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,05%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,69%</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>13050</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>157</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>106375</v>
+          <t>7853</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>20062</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>7,2%</t>
+        </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>22640</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>15253</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>30894</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -1606,70 +2196,112 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>865</v>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>618068</v>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>723</t>
+        </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>897</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>702869</v>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="n">
-        <v>1762</v>
-      </c>
-      <c r="N17" s="2" t="n">
-        <v>1320937</v>
+          <t>1160</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>9220</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>4623</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>1855</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>9721</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -1677,75 +2309,686 @@
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>942</v>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>665340</v>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>157649</t>
+        </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>152356</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>162081</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>977</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>761972</v>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>90,71%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>96,5%</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>216</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>164288</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>1919</v>
-      </c>
-      <c r="N18" s="2" t="n">
-        <v>1427312</v>
+          <t>156113</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>170686</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>90,65%</t>
+        </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>321938</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>312565</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>330015</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>92,19%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>89,51%</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>94,51%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>167962</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>167962</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>167962</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>181238</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>181238</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>181238</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>349201</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>349201</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>349201</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún síntoma</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>32551</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>23273</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>42140</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>45535</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>33747</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>7,72%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>78086</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>63860</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>95162</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>5,47%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>4,47%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>6,67%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Sí, por algún dolor</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>14721</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>9220</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>22171</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>13568</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>8264</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>21555</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>28290</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>20251</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>38405</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>2,69%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>618068</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>606023</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>629362</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>92,9%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>91,08%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>94,59%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>702869</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>687116</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>714365</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>92,24%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>90,18%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>93,75%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1762</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1320937</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>1300177</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>1337647</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>92,55%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>91,09%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>93,72%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>665340</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>665340</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>665340</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>761972</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1427312</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>1427312</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>1427312</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1753,15 +2996,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="J1:P1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/IP12_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP12_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2283</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8474</t>
+          <t>8747</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13346</t>
+          <t>13637</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>19074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,4%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9552</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424</t>
+          <t>439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>11722</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>101971</t>
+          <t>102872</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>112252</t>
+          <t>111991</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>124561</t>
+          <t>124719</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135476</t>
+          <t>135524</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>232492</t>
+          <t>232093</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>245924</t>
+          <t>245799</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16298</t>
+          <t>15794</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20041</t>
+          <t>19507</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15954</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32106</t>
+          <t>31960</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,17%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7556</t>
+          <t>7780</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9341</t>
+          <t>9130</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4083</t>
+          <t>4264</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14476</t>
+          <t>14177</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>170378</t>
+          <t>170166</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>182026</t>
+          <t>181763</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>229821</t>
+          <t>229951</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>243863</t>
+          <t>243894</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>404875</t>
+          <t>404142</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>422959</t>
+          <t>422504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,83%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14150</t>
+          <t>14912</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22832</t>
+          <t>21709</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>13318</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32763</t>
+          <t>31676</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2761</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5502</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17105</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167932</t>
+          <t>167097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>181530</t>
+          <t>181306</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>158381</t>
+          <t>159780</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175179</t>
+          <t>176114</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,48%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>331975</t>
+          <t>331244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>353215</t>
+          <t>353823</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>15273</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7853</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>20713</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15253</t>
+          <t>16001</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30894</t>
+          <t>31627</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3634</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1342</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>152356</t>
+          <t>151911</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>162081</t>
+          <t>161963</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>156113</t>
+          <t>156271</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>170686</t>
+          <t>170277</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>312565</t>
+          <t>312230</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>330015</t>
+          <t>329459</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,35%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23273</t>
+          <t>24459</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42140</t>
+          <t>42378</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33747</t>
+          <t>34598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58792</t>
+          <t>59646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>63860</t>
+          <t>65252</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95162</t>
+          <t>95291</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22171</t>
+          <t>21824</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21555</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20251</t>
+          <t>20271</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>38237</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>606023</t>
+          <t>606801</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>629362</t>
+          <t>628324</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>687116</t>
+          <t>689239</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>714365</t>
+          <t>716087</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1300177</t>
+          <t>1301380</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1337647</t>
+          <t>1337289</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP12_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP12_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6918</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3140</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12437</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4557</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2283</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8747</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>4719</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3659</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13637</t>
+          <t>8813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19074</t>
+          <t>18127</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4153</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4295</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1810</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9085</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>4378</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>11616</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>117539</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>111694</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121679</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>93,35%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>88,71%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>96,64%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>108427</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>102872</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>111991</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>92,45%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>87,71%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>131557</t>
+          <t>111975</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>124719</t>
+          <t>105915</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>135524</t>
+          <t>115870</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>239986</t>
+          <t>229514</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>232093</t>
+          <t>221572</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>245799</t>
+          <t>235060</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12352</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7572</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>19812</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,21%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,35%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9833</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5716</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>15794</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19507</t>
+          <t>15049</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>22942</t>
+          <t>21460</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16631</t>
+          <t>15054</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31960</t>
+          <t>29391</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>3953</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>9145</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,86%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3759</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>1556</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>7780</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4113</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1124</t>
+          <t>1562</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>9130</t>
+          <t>8183</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4264</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>220900</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>212733</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>225938</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>93,13%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>89,68%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>176920</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>170166</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>181763</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>92,87%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>89,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>237813</t>
+          <t>171688</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>229951</t>
+          <t>164622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>243894</t>
+          <t>176112</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>414734</t>
+          <t>392588</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>404142</t>
+          <t>383209</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>422504</t>
+          <t>399219</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11552</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>5884</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>22332</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,86%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13,27%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>8570</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4447</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>14912</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,52%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,87%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>4800</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21709</t>
+          <t>15018</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>20568</t>
+          <t>20234</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13318</t>
+          <t>12676</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31676</t>
+          <t>29449</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -1745,72 +1745,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3930</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8971</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>5944</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2761</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11679</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3,14%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4080</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>11470</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>16710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>152858</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>142578</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>158860</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,8%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,7%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>175071</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>167097</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>181306</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>92,34%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>88,14%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,63%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>169209</t>
+          <t>141555</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>159780</t>
+          <t>134317</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176114</t>
+          <t>147085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>344279</t>
+          <t>294413</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>331244</t>
+          <t>283419</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>353823</t>
+          <t>303394</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,48%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11454</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7356</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18303</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,76%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,34%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>9590</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5466</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15273</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13050</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7967</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20713</t>
+          <t>15346</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>20937</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16001</t>
+          <t>14770</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31627</t>
+          <t>28195</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -2201,72 +2201,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>8400</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>723</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3345</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3516</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3900</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1342</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>9209</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4490</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2314,72 +2314,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>154127</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>147260</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>159081</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>91,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>86,94%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>157649</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>151911</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>161963</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>93,86%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>90,44%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>96,43%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>164288</t>
+          <t>156967</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>156271</t>
+          <t>150897</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>170277</t>
+          <t>161010</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>321938</t>
+          <t>311094</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>312230</t>
+          <t>302572</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>329459</t>
+          <t>317871</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>42278</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>31638</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>56786</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>6,03%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>32551</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>24459</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>42378</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>45535</t>
+          <t>31990</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34598</t>
+          <t>24045</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59646</t>
+          <t>41922</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>78086</t>
+          <t>74268</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65252</t>
+          <t>61127</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>95291</t>
+          <t>91555</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -2657,72 +2657,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>13127</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>7972</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>20665</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1,87%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>14721</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>9523</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>21824</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>14659</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7886</t>
+          <t>9434</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>27785</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>20271</t>
+          <t>19773</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>38237</t>
+          <t>37784</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -2770,72 +2770,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>645425</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>630717</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>657163</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>92,09%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>90,0%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>93,77%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>865</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>618068</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>606801</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>628324</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>92,9%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>91,2%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>702869</t>
+          <t>582184</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>689239</t>
+          <t>569808</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>716087</t>
+          <t>592488</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1320937</t>
+          <t>1227609</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1301380</t>
+          <t>1209389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1337289</t>
+          <t>1243691</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
